--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/53.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/53.xlsx
@@ -426,13 +426,13 @@
         <v>-0.696142762942036</v>
       </c>
       <c r="E2">
-        <v>-19.731536950039</v>
+        <v>-26.48415738115463</v>
       </c>
       <c r="F2">
-        <v>-8.047295807240245</v>
+        <v>-8.811176559228519</v>
       </c>
       <c r="G2">
-        <v>-13.67157099583317</v>
+        <v>-17.20530358372541</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>0.1898644401422134</v>
       </c>
       <c r="E3">
-        <v>-19.65519593521769</v>
+        <v>-25.78337149999363</v>
       </c>
       <c r="F3">
-        <v>-7.764495025626137</v>
+        <v>-9.096086441195512</v>
       </c>
       <c r="G3">
-        <v>-13.92222564079355</v>
+        <v>-16.866806923426</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>0.949203200375322</v>
       </c>
       <c r="E4">
-        <v>-22.01532337616529</v>
+        <v>-26.16449240095318</v>
       </c>
       <c r="F4">
-        <v>-7.989336921852907</v>
+        <v>-8.342882242636172</v>
       </c>
       <c r="G4">
-        <v>-13.50636318651415</v>
+        <v>-17.33535008887183</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>1.445095715399583</v>
       </c>
       <c r="E5">
-        <v>-21.21408235609214</v>
+        <v>-24.97727595578426</v>
       </c>
       <c r="F5">
-        <v>-8.020840395849307</v>
+        <v>-8.133278368801282</v>
       </c>
       <c r="G5">
-        <v>-13.36322016321438</v>
+        <v>-16.50183748572182</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>1.702511152623715</v>
       </c>
       <c r="E6">
-        <v>-21.61002042400478</v>
+        <v>-28.00561596435568</v>
       </c>
       <c r="F6">
-        <v>-8.046775955773501</v>
+        <v>-8.993720046012774</v>
       </c>
       <c r="G6">
-        <v>-13.82277023170277</v>
+        <v>-18.74468243039496</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>1.724745528843592</v>
       </c>
       <c r="E7">
-        <v>-22.95276730896714</v>
+        <v>-27.40048956813272</v>
       </c>
       <c r="F7">
-        <v>-7.991489970044946</v>
+        <v>-9.190878366911182</v>
       </c>
       <c r="G7">
-        <v>-13.8296644427883</v>
+        <v>-17.64151430616193</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>1.557410899559588</v>
       </c>
       <c r="E8">
-        <v>-24.27189367350548</v>
+        <v>-29.15330335991165</v>
       </c>
       <c r="F8">
-        <v>-7.929527476103378</v>
+        <v>-8.145577033014106</v>
       </c>
       <c r="G8">
-        <v>-14.23309248802219</v>
+        <v>-16.63935423687761</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>1.248472026358852</v>
       </c>
       <c r="E9">
-        <v>-23.03558857009342</v>
+        <v>-27.95221167038323</v>
       </c>
       <c r="F9">
-        <v>-7.666745925039862</v>
+        <v>-7.909190316590262</v>
       </c>
       <c r="G9">
-        <v>-13.95839500608286</v>
+        <v>-17.27721525392946</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>0.8634800565719534</v>
       </c>
       <c r="E10">
-        <v>-24.09560923733489</v>
+        <v>-29.13901149594344</v>
       </c>
       <c r="F10">
-        <v>-8.226925671066569</v>
+        <v>-8.239160987042775</v>
       </c>
       <c r="G10">
-        <v>-14.29236284008454</v>
+        <v>-17.84981548676565</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>0.4647545754708815</v>
       </c>
       <c r="E11">
-        <v>-24.25758369564124</v>
+        <v>-29.69374050493504</v>
       </c>
       <c r="F11">
-        <v>-7.527645075222027</v>
+        <v>-8.314204099992915</v>
       </c>
       <c r="G11">
-        <v>-14.52298868453232</v>
+        <v>-18.50735107595738</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>0.1115341090558379</v>
       </c>
       <c r="E12">
-        <v>-25.14272828212851</v>
+        <v>-28.31440354999071</v>
       </c>
       <c r="F12">
-        <v>-7.829528325337742</v>
+        <v>-8.186298467291323</v>
       </c>
       <c r="G12">
-        <v>-13.94392626680347</v>
+        <v>-18.8027593307904</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-0.1497718158916293</v>
       </c>
       <c r="E13">
-        <v>-24.58287304056022</v>
+        <v>-31.53403535759414</v>
       </c>
       <c r="F13">
-        <v>-7.311570179016652</v>
+        <v>-7.812270681977199</v>
       </c>
       <c r="G13">
-        <v>-14.39306135902532</v>
+        <v>-17.97151114078926</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-0.2896902826493177</v>
       </c>
       <c r="E14">
-        <v>-24.90442186594886</v>
+        <v>-29.79743803123668</v>
       </c>
       <c r="F14">
-        <v>-7.128488628147626</v>
+        <v>-8.721119122347055</v>
       </c>
       <c r="G14">
-        <v>-13.1149093844958</v>
+        <v>-17.25033858996888</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-0.2980585120500652</v>
       </c>
       <c r="E15">
-        <v>-24.39499118245599</v>
+        <v>-31.93767183131983</v>
       </c>
       <c r="F15">
-        <v>-7.191659093776196</v>
+        <v>-8.564812099610927</v>
       </c>
       <c r="G15">
-        <v>-13.08789533289535</v>
+        <v>-17.17815545503061</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-0.1843792058833234</v>
       </c>
       <c r="E16">
-        <v>-26.30600721369288</v>
+        <v>-31.74071491130422</v>
       </c>
       <c r="F16">
-        <v>-7.022644414774583</v>
+        <v>-7.728702876010727</v>
       </c>
       <c r="G16">
-        <v>-12.83075532922354</v>
+        <v>-16.83477905060633</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>0.02401735557710934</v>
       </c>
       <c r="E17">
-        <v>-25.9908707074991</v>
+        <v>-32.46626248833915</v>
       </c>
       <c r="F17">
-        <v>-6.811138114208772</v>
+        <v>-7.688952253459676</v>
       </c>
       <c r="G17">
-        <v>-12.34872334597796</v>
+        <v>-16.21317612269784</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>0.2877632823097802</v>
       </c>
       <c r="E18">
-        <v>-25.78511949096059</v>
+        <v>-31.17706933699151</v>
       </c>
       <c r="F18">
-        <v>-6.786667878182838</v>
+        <v>-7.93980929083289</v>
       </c>
       <c r="G18">
-        <v>-11.99710368316089</v>
+        <v>-17.62315402060113</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>0.5613694327868686</v>
       </c>
       <c r="E19">
-        <v>-28.47398697402101</v>
+        <v>-32.74607010456209</v>
       </c>
       <c r="F19">
-        <v>-6.381023779825839</v>
+        <v>-7.388032292467027</v>
       </c>
       <c r="G19">
-        <v>-11.82066153755435</v>
+        <v>-16.72833011406383</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>0.8001476913856919</v>
       </c>
       <c r="E20">
-        <v>-28.68735508384042</v>
+        <v>-33.67808213279174</v>
       </c>
       <c r="F20">
-        <v>-6.488401020525028</v>
+        <v>-7.562431967507613</v>
       </c>
       <c r="G20">
-        <v>-10.78535794160361</v>
+        <v>-16.17325921985808</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>0.9682820099114919</v>
       </c>
       <c r="E21">
-        <v>-28.95170475403818</v>
+        <v>-33.97269559478276</v>
       </c>
       <c r="F21">
-        <v>-5.957201509044949</v>
+        <v>-7.22513744904915</v>
       </c>
       <c r="G21">
-        <v>-11.76252504733921</v>
+        <v>-16.74714394436351</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>1.039190375343402</v>
       </c>
       <c r="E22">
-        <v>-28.43467529116043</v>
+        <v>-34.75252825398465</v>
       </c>
       <c r="F22">
-        <v>-6.074072670780718</v>
+        <v>-6.474050269372274</v>
       </c>
       <c r="G22">
-        <v>-11.32720486165274</v>
+        <v>-15.9396290553334</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>1.001516930174319</v>
       </c>
       <c r="E23">
-        <v>-29.42968292131078</v>
+        <v>-36.5263134088931</v>
       </c>
       <c r="F23">
-        <v>-5.55660309773454</v>
+        <v>-6.366448142433093</v>
       </c>
       <c r="G23">
-        <v>-10.90359738608422</v>
+        <v>-16.12459585570356</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>0.8543975222828472</v>
       </c>
       <c r="E24">
-        <v>-30.75990631140492</v>
+        <v>-34.48821934005296</v>
       </c>
       <c r="F24">
-        <v>-5.714253103086961</v>
+        <v>-6.610199883216688</v>
       </c>
       <c r="G24">
-        <v>-12.1354911077935</v>
+        <v>-15.68259829966439</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>0.6105786378332888</v>
       </c>
       <c r="E25">
-        <v>-30.30078244566325</v>
+        <v>-35.23442355127388</v>
       </c>
       <c r="F25">
-        <v>-5.46282157639292</v>
+        <v>-6.393182681991626</v>
       </c>
       <c r="G25">
-        <v>-10.95531803904425</v>
+        <v>-16.69232462077872</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>0.2907804786774926</v>
       </c>
       <c r="E26">
-        <v>-28.57021704668401</v>
+        <v>-36.39608128914351</v>
       </c>
       <c r="F26">
-        <v>-5.374901350644341</v>
+        <v>-7.000573889137019</v>
       </c>
       <c r="G26">
-        <v>-11.9902177484392</v>
+        <v>-15.39362740063248</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-0.07642946041753654</v>
       </c>
       <c r="E27">
-        <v>-30.8266107335379</v>
+        <v>-34.09400662073724</v>
       </c>
       <c r="F27">
-        <v>-5.407798881772807</v>
+        <v>-6.895181427876355</v>
       </c>
       <c r="G27">
-        <v>-12.34253593636506</v>
+        <v>-16.9818417598246</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-0.4593846652154639</v>
       </c>
       <c r="E28">
-        <v>-30.66861001117328</v>
+        <v>-34.78615896620261</v>
       </c>
       <c r="F28">
-        <v>-5.187967831062489</v>
+        <v>-6.440215976194826</v>
       </c>
       <c r="G28">
-        <v>-11.48489276677931</v>
+        <v>-15.6790378079369</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-0.8250026188155268</v>
       </c>
       <c r="E29">
-        <v>-31.0687844665201</v>
+        <v>-37.53027383215661</v>
       </c>
       <c r="F29">
-        <v>-5.373723073443255</v>
+        <v>-6.516627411055905</v>
       </c>
       <c r="G29">
-        <v>-12.35091492712495</v>
+        <v>-15.58730590158924</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-1.142445188381773</v>
       </c>
       <c r="E30">
-        <v>-30.5136433663938</v>
+        <v>-35.39948869309048</v>
       </c>
       <c r="F30">
-        <v>-5.309894182080341</v>
+        <v>-6.045352164004224</v>
       </c>
       <c r="G30">
-        <v>-12.39125723506651</v>
+        <v>-16.52625110380118</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-1.384579526685293</v>
       </c>
       <c r="E31">
-        <v>-29.4045430978572</v>
+        <v>-36.558725961603</v>
       </c>
       <c r="F31">
-        <v>-5.242688829705711</v>
+        <v>-6.071086593277157</v>
       </c>
       <c r="G31">
-        <v>-11.69826404787641</v>
+        <v>-17.78056880572071</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-1.531680993181742</v>
       </c>
       <c r="E32">
-        <v>-30.45295955045401</v>
+        <v>-35.10097395074185</v>
       </c>
       <c r="F32">
-        <v>-5.384904829059215</v>
+        <v>-6.51182323916142</v>
       </c>
       <c r="G32">
-        <v>-12.88406835458796</v>
+        <v>-14.6903632459068</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-1.570990771766489</v>
       </c>
       <c r="E33">
-        <v>-30.28660832201924</v>
+        <v>-36.94068236601696</v>
       </c>
       <c r="F33">
-        <v>-5.47885105581604</v>
+        <v>-6.931098690259085</v>
       </c>
       <c r="G33">
-        <v>-11.91243648099402</v>
+        <v>-16.65467047581505</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-1.500380346777328</v>
       </c>
       <c r="E34">
-        <v>-29.68912598992123</v>
+        <v>-34.87519555790442</v>
       </c>
       <c r="F34">
-        <v>-4.892224212854453</v>
+        <v>-5.695373744869006</v>
       </c>
       <c r="G34">
-        <v>-11.987208462544</v>
+        <v>-16.55920923991739</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-1.325179737457486</v>
       </c>
       <c r="E35">
-        <v>-29.64812518625578</v>
+        <v>-34.82677937805141</v>
       </c>
       <c r="F35">
-        <v>-5.32633384133556</v>
+        <v>-6.673868028429185</v>
       </c>
       <c r="G35">
-        <v>-12.27549407864928</v>
+        <v>-17.9593796466606</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-1.059627020678871</v>
       </c>
       <c r="E36">
-        <v>-28.38404242328066</v>
+        <v>-35.56839398086557</v>
       </c>
       <c r="F36">
-        <v>-5.135659608381439</v>
+        <v>-6.645481683600848</v>
       </c>
       <c r="G36">
-        <v>-12.5302074524408</v>
+        <v>-15.85036516068526</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-0.7137541955646481</v>
       </c>
       <c r="E37">
-        <v>-28.9379653638989</v>
+        <v>-35.22651457141949</v>
       </c>
       <c r="F37">
-        <v>-5.690982128365493</v>
+        <v>-6.551371147355296</v>
       </c>
       <c r="G37">
-        <v>-12.97879299410313</v>
+        <v>-17.12622458242884</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-0.3008779775243885</v>
       </c>
       <c r="E38">
-        <v>-27.90636087105556</v>
+        <v>-35.70994049292332</v>
       </c>
       <c r="F38">
-        <v>-5.106155167176802</v>
+        <v>-5.75502877929178</v>
       </c>
       <c r="G38">
-        <v>-12.50670257911198</v>
+        <v>-16.30238539334458</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>0.1664396647455626</v>
       </c>
       <c r="E39">
-        <v>-27.99613786825763</v>
+        <v>-33.81279517757192</v>
       </c>
       <c r="F39">
-        <v>-5.579021246820544</v>
+        <v>-6.229948133654888</v>
       </c>
       <c r="G39">
-        <v>-12.03924361733027</v>
+        <v>-15.91451360159972</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>0.6644789339925323</v>
       </c>
       <c r="E40">
-        <v>-26.70650545493124</v>
+        <v>-33.57601938560687</v>
       </c>
       <c r="F40">
-        <v>-5.205030678595433</v>
+        <v>-5.712284556634069</v>
       </c>
       <c r="G40">
-        <v>-12.03547290596104</v>
+        <v>-16.79239744661258</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>1.170274640742835</v>
       </c>
       <c r="E41">
-        <v>-27.16955550763756</v>
+        <v>-31.88250596095839</v>
       </c>
       <c r="F41">
-        <v>-5.429984226089241</v>
+        <v>-5.928688467743377</v>
       </c>
       <c r="G41">
-        <v>-12.16868925846131</v>
+        <v>-16.43318173705565</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>1.656215835908932</v>
       </c>
       <c r="E42">
-        <v>-27.45975823594511</v>
+        <v>-33.44764620443743</v>
       </c>
       <c r="F42">
-        <v>-5.13468008627274</v>
+        <v>-6.481750247533141</v>
       </c>
       <c r="G42">
-        <v>-11.92610572352567</v>
+        <v>-16.43123679155132</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>2.106955056808233</v>
       </c>
       <c r="E43">
-        <v>-26.01268889526805</v>
+        <v>-33.0384895208964</v>
       </c>
       <c r="F43">
-        <v>-4.908982196998676</v>
+        <v>-5.844474905689884</v>
       </c>
       <c r="G43">
-        <v>-11.94749515825491</v>
+        <v>-14.85994759642873</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>2.511283175407772</v>
       </c>
       <c r="E44">
-        <v>-25.60787954677438</v>
+        <v>-33.49927760083588</v>
       </c>
       <c r="F44">
-        <v>-5.23271544170323</v>
+        <v>-5.874596992201543</v>
       </c>
       <c r="G44">
-        <v>-12.30945034424558</v>
+        <v>-17.02701911952627</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>2.865892854190447</v>
       </c>
       <c r="E45">
-        <v>-27.12024042569403</v>
+        <v>-31.86123571854436</v>
       </c>
       <c r="F45">
-        <v>-5.405744815200483</v>
+        <v>-6.948742361936517</v>
       </c>
       <c r="G45">
-        <v>-12.09420529437325</v>
+        <v>-15.40067720735836</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>3.168342580481025</v>
       </c>
       <c r="E46">
-        <v>-25.37601262063365</v>
+        <v>-32.57263181430532</v>
       </c>
       <c r="F46">
-        <v>-5.082508062300418</v>
+        <v>-6.114563675847237</v>
       </c>
       <c r="G46">
-        <v>-11.67225971266544</v>
+        <v>-15.80950144182127</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>3.416486398346865</v>
       </c>
       <c r="E47">
-        <v>-25.12329207168759</v>
+        <v>-33.87185779981696</v>
       </c>
       <c r="F47">
-        <v>-5.402649461988756</v>
+        <v>-5.991662949764911</v>
       </c>
       <c r="G47">
-        <v>-12.38623513748344</v>
+        <v>-16.24962357381245</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>3.61091362998518</v>
       </c>
       <c r="E48">
-        <v>-24.55171713938745</v>
+        <v>-33.18405731787296</v>
       </c>
       <c r="F48">
-        <v>-5.172945588601588</v>
+        <v>-6.266271220678449</v>
       </c>
       <c r="G48">
-        <v>-11.84699030622817</v>
+        <v>-18.53930446150243</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>3.751829118939982</v>
       </c>
       <c r="E49">
-        <v>-25.13852585824939</v>
+        <v>-32.27805005163236</v>
       </c>
       <c r="F49">
-        <v>-5.220417173416886</v>
+        <v>-6.302036051366819</v>
       </c>
       <c r="G49">
-        <v>-11.89614528639527</v>
+        <v>-15.27911397515632</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>3.846298957681459</v>
       </c>
       <c r="E50">
-        <v>-24.61721698743439</v>
+        <v>-30.66087764180518</v>
       </c>
       <c r="F50">
-        <v>-5.598064518600745</v>
+        <v>-6.912499647988164</v>
       </c>
       <c r="G50">
-        <v>-11.78287166022357</v>
+        <v>-16.23795224551375</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>3.899140080724463</v>
       </c>
       <c r="E51">
-        <v>-23.86346607427969</v>
+        <v>-29.44901724108653</v>
       </c>
       <c r="F51">
-        <v>-5.480939963918505</v>
+        <v>-6.531509099616811</v>
       </c>
       <c r="G51">
-        <v>-11.86305638373025</v>
+        <v>-15.90907768582424</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>3.920202541528842</v>
       </c>
       <c r="E52">
-        <v>-23.15594182379528</v>
+        <v>-28.66260244491449</v>
       </c>
       <c r="F52">
-        <v>-5.339287763870897</v>
+        <v>-6.298295733921029</v>
       </c>
       <c r="G52">
-        <v>-11.15925757589998</v>
+        <v>-15.65931854343223</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>3.915276933322106</v>
       </c>
       <c r="E53">
-        <v>-23.28916952910094</v>
+        <v>-30.70998441394436</v>
       </c>
       <c r="F53">
-        <v>-5.447037571386693</v>
+        <v>-6.64718931450417</v>
       </c>
       <c r="G53">
-        <v>-11.20083471732768</v>
+        <v>-15.73209095547649</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>3.890318166415483</v>
       </c>
       <c r="E54">
-        <v>-23.49372070002741</v>
+        <v>-29.70557114328008</v>
       </c>
       <c r="F54">
-        <v>-5.618586179853009</v>
+        <v>-6.566562450422669</v>
       </c>
       <c r="G54">
-        <v>-11.7702551711734</v>
+        <v>-15.56502427483717</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>3.848272857412674</v>
       </c>
       <c r="E55">
-        <v>-23.35511769607464</v>
+        <v>-29.4619324489564</v>
       </c>
       <c r="F55">
-        <v>-5.92757987360257</v>
+        <v>-6.524660363385494</v>
       </c>
       <c r="G55">
-        <v>-11.48740878138915</v>
+        <v>-16.1321273468054</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>3.789641023504575</v>
       </c>
       <c r="E56">
-        <v>-20.69641890685332</v>
+        <v>-30.57925189781692</v>
       </c>
       <c r="F56">
-        <v>-5.400530463473898</v>
+        <v>-6.220848159464773</v>
       </c>
       <c r="G56">
-        <v>-12.01141186098162</v>
+        <v>-16.26029180681275</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>3.715864516183961</v>
       </c>
       <c r="E57">
-        <v>-22.39409852758886</v>
+        <v>-27.86489816304134</v>
       </c>
       <c r="F57">
-        <v>-5.042586795436979</v>
+        <v>-7.035425713365138</v>
       </c>
       <c r="G57">
-        <v>-12.04769875063757</v>
+        <v>-15.91407826486131</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>3.625012694473603</v>
       </c>
       <c r="E58">
-        <v>-21.59113215891879</v>
+        <v>-28.05775228560599</v>
       </c>
       <c r="F58">
-        <v>-5.820557778954917</v>
+        <v>-6.202068178793013</v>
       </c>
       <c r="G58">
-        <v>-11.35982366685118</v>
+        <v>-15.74736250204915</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>3.517373622933871</v>
       </c>
       <c r="E59">
-        <v>-22.94052684372441</v>
+        <v>-30.83146072920012</v>
       </c>
       <c r="F59">
-        <v>-5.814484266769208</v>
+        <v>-7.004105157401971</v>
       </c>
       <c r="G59">
-        <v>-11.73378620151279</v>
+        <v>-17.29085470155125</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>3.391519896829654</v>
       </c>
       <c r="E60">
-        <v>-22.21100326651073</v>
+        <v>-27.98922288844792</v>
       </c>
       <c r="F60">
-        <v>-5.32827863219972</v>
+        <v>-6.601577000433599</v>
       </c>
       <c r="G60">
-        <v>-11.92167952413967</v>
+        <v>-16.79474462339992</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>3.249734835022657</v>
       </c>
       <c r="E61">
-        <v>-21.91871744015966</v>
+        <v>-28.12094714038303</v>
       </c>
       <c r="F61">
-        <v>-5.768506116632169</v>
+        <v>-7.065457528639615</v>
       </c>
       <c r="G61">
-        <v>-12.74317815752766</v>
+        <v>-16.30052817729705</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>3.094342969885625</v>
       </c>
       <c r="E62">
-        <v>-21.12908742744218</v>
+        <v>-26.86299593121431</v>
       </c>
       <c r="F62">
-        <v>-5.658055298677591</v>
+        <v>-7.259403698015034</v>
       </c>
       <c r="G62">
-        <v>-10.892957292721</v>
+        <v>-17.17134069703802</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>2.930715758161511</v>
       </c>
       <c r="E63">
-        <v>-21.03952779699248</v>
+        <v>-26.17625737642511</v>
       </c>
       <c r="F63">
-        <v>-5.744603243250442</v>
+        <v>-6.1287588278938</v>
       </c>
       <c r="G63">
-        <v>-11.7245133634573</v>
+        <v>-17.08111839945627</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>2.764218055418293</v>
       </c>
       <c r="E64">
-        <v>-20.41006085297829</v>
+        <v>-30.50645441390662</v>
       </c>
       <c r="F64">
-        <v>-5.890748416980152</v>
+        <v>-6.832393427226363</v>
       </c>
       <c r="G64">
-        <v>-11.87514318549414</v>
+        <v>-16.28739524314276</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>2.601068403598356</v>
       </c>
       <c r="E65">
-        <v>-20.65943938810669</v>
+        <v>-29.43926517231101</v>
       </c>
       <c r="F65">
-        <v>-5.532608369409718</v>
+        <v>-6.643379313998102</v>
       </c>
       <c r="G65">
-        <v>-11.83802203836229</v>
+        <v>-16.81552326247715</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>2.448096908053085</v>
       </c>
       <c r="E66">
-        <v>-20.06064379854644</v>
+        <v>-28.63324887639677</v>
       </c>
       <c r="F66">
-        <v>-5.894987205862825</v>
+        <v>-6.394706998935237</v>
       </c>
       <c r="G66">
-        <v>-12.68818668557482</v>
+        <v>-16.38031232479349</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>2.313503803589427</v>
       </c>
       <c r="E67">
-        <v>-20.2631797985395</v>
+        <v>-29.05352296362664</v>
       </c>
       <c r="F67">
-        <v>-5.869788861042268</v>
+        <v>-6.898261735881884</v>
       </c>
       <c r="G67">
-        <v>-12.26243066595131</v>
+        <v>-15.86957956699519</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>2.205893446329851</v>
       </c>
       <c r="E68">
-        <v>-22.13441318561901</v>
+        <v>-27.4480657160573</v>
       </c>
       <c r="F68">
-        <v>-5.738998508015702</v>
+        <v>-6.643940341818647</v>
       </c>
       <c r="G68">
-        <v>-12.58046484427248</v>
+        <v>-15.26950511672859</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>2.131635379182837</v>
       </c>
       <c r="E69">
-        <v>-21.40528811411801</v>
+        <v>-29.84234011525974</v>
       </c>
       <c r="F69">
-        <v>-5.938482896977412</v>
+        <v>-6.608936481822646</v>
       </c>
       <c r="G69">
-        <v>-12.76728555014463</v>
+        <v>-16.43095705045326</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>2.097411066546192</v>
       </c>
       <c r="E70">
-        <v>-20.82008700352879</v>
+        <v>-27.7259011818499</v>
       </c>
       <c r="F70">
-        <v>-5.688589940580222</v>
+        <v>-7.040433391469757</v>
       </c>
       <c r="G70">
-        <v>-11.9703313013848</v>
+        <v>-16.3458478904569</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>2.105945428914704</v>
       </c>
       <c r="E71">
-        <v>-21.09032821841053</v>
+        <v>-28.25467297782954</v>
       </c>
       <c r="F71">
-        <v>-6.072470752247251</v>
+        <v>-6.991903495176467</v>
       </c>
       <c r="G71">
-        <v>-12.22070454997434</v>
+        <v>-16.70971491649651</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>2.159790209238459</v>
       </c>
       <c r="E72">
-        <v>-20.93457135491671</v>
+        <v>-28.35774104624412</v>
       </c>
       <c r="F72">
-        <v>-5.772889814606105</v>
+        <v>-6.49449868422595</v>
       </c>
       <c r="G72">
-        <v>-12.28936857500436</v>
+        <v>-17.06416344047689</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>2.255061570050207</v>
       </c>
       <c r="E73">
-        <v>-21.1391949814273</v>
+        <v>-28.49216879716181</v>
       </c>
       <c r="F73">
-        <v>-6.156371136455966</v>
+        <v>-6.898730512832855</v>
       </c>
       <c r="G73">
-        <v>-11.59133011641241</v>
+        <v>-17.76897030942387</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>2.386352281468579</v>
       </c>
       <c r="E74">
-        <v>-21.13449895388134</v>
+        <v>-28.16741834064975</v>
       </c>
       <c r="F74">
-        <v>-6.173335794222153</v>
+        <v>-6.511522730963966</v>
       </c>
       <c r="G74">
-        <v>-12.68373731237004</v>
+        <v>-15.65353833092066</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>2.543991699777882</v>
       </c>
       <c r="E75">
-        <v>-21.94478333654781</v>
+        <v>-29.62222457916891</v>
       </c>
       <c r="F75">
-        <v>-6.070548925118866</v>
+        <v>-7.223770314917647</v>
       </c>
       <c r="G75">
-        <v>-12.03449629502695</v>
+        <v>-17.53669912384307</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>2.719310239965101</v>
       </c>
       <c r="E76">
-        <v>-23.25159225178529</v>
+        <v>-29.56726022590081</v>
       </c>
       <c r="F76">
-        <v>-6.177567852354686</v>
+        <v>-7.336043186527938</v>
       </c>
       <c r="G76">
-        <v>-12.12456299696836</v>
+        <v>-17.26815594606124</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>2.900843428544391</v>
       </c>
       <c r="E77">
-        <v>-22.51048936653401</v>
+        <v>-30.24221342708505</v>
       </c>
       <c r="F77">
-        <v>-6.787997003372371</v>
+        <v>-7.568174881083475</v>
       </c>
       <c r="G77">
-        <v>-12.14354897563608</v>
+        <v>-16.76754683652204</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>3.079710234622706</v>
       </c>
       <c r="E78">
-        <v>-22.60696850526742</v>
+        <v>-28.55214843539341</v>
       </c>
       <c r="F78">
-        <v>-6.518742450305975</v>
+        <v>-7.158887467268008</v>
       </c>
       <c r="G78">
-        <v>-11.5994045369827</v>
+        <v>-16.77786249642241</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>3.244606238846581</v>
       </c>
       <c r="E79">
-        <v>-22.47921119656302</v>
+        <v>-31.01850481961294</v>
       </c>
       <c r="F79">
-        <v>-6.553180927290164</v>
+        <v>-7.356259192538523</v>
       </c>
       <c r="G79">
-        <v>-11.81127614095051</v>
+        <v>-16.19800389249136</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>3.389784415674205</v>
       </c>
       <c r="E80">
-        <v>-23.6390666017776</v>
+        <v>-29.86118762407967</v>
       </c>
       <c r="F80">
-        <v>-6.372899764406114</v>
+        <v>-7.133411973912249</v>
       </c>
       <c r="G80">
-        <v>-11.81272947044225</v>
+        <v>-14.99721936721461</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>3.509330952980721</v>
       </c>
       <c r="E81">
-        <v>-23.82435364427544</v>
+        <v>-32.2415301729975</v>
       </c>
       <c r="F81">
-        <v>-6.438864679122477</v>
+        <v>-7.520504541175789</v>
       </c>
       <c r="G81">
-        <v>-11.59629262417578</v>
+        <v>-16.20585981705605</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>3.602010181914415</v>
       </c>
       <c r="E82">
-        <v>-24.70650038096962</v>
+        <v>-32.82112729700223</v>
       </c>
       <c r="F82">
-        <v>-6.598517676531449</v>
+        <v>-7.48694858431298</v>
       </c>
       <c r="G82">
-        <v>-10.92636400775779</v>
+        <v>-14.16592482957592</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>3.666345376287071</v>
       </c>
       <c r="E83">
-        <v>-24.92806955721692</v>
+        <v>-32.53473527957213</v>
       </c>
       <c r="F83">
-        <v>-6.791112548834519</v>
+        <v>-7.778119251690184</v>
       </c>
       <c r="G83">
-        <v>-11.49032868255479</v>
+        <v>-14.13168551233601</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>3.702039922818613</v>
       </c>
       <c r="E84">
-        <v>-26.10829403851799</v>
+        <v>-32.01503401702986</v>
       </c>
       <c r="F84">
-        <v>-6.777573842889906</v>
+        <v>-7.47399901696891</v>
       </c>
       <c r="G84">
-        <v>-11.60116905775513</v>
+        <v>-15.42099733587841</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>3.70963480591228</v>
       </c>
       <c r="E85">
-        <v>-27.42088581506327</v>
+        <v>-33.02376971613447</v>
       </c>
       <c r="F85">
-        <v>-6.851559832141491</v>
+        <v>-7.194142740578084</v>
       </c>
       <c r="G85">
-        <v>-11.58553335117315</v>
+        <v>-16.83629196991777</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>3.688090084720906</v>
       </c>
       <c r="E86">
-        <v>-28.19784515750728</v>
+        <v>-36.17460268237637</v>
       </c>
       <c r="F86">
-        <v>-6.911807964429595</v>
+        <v>-7.253261294622003</v>
       </c>
       <c r="G86">
-        <v>-11.96412733904421</v>
+        <v>-15.19265411257995</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>3.63757588904621</v>
       </c>
       <c r="E87">
-        <v>-28.0710976985066</v>
+        <v>-35.43695502279294</v>
       </c>
       <c r="F87">
-        <v>-7.063265679652647</v>
+        <v>-8.331886968391755</v>
       </c>
       <c r="G87">
-        <v>-10.11054295996965</v>
+        <v>-15.2694008345441</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>3.555499567554429</v>
       </c>
       <c r="E88">
-        <v>-29.1368649992638</v>
+        <v>-34.88300491133065</v>
       </c>
       <c r="F88">
-        <v>-6.575518307374479</v>
+        <v>-7.973130067367257</v>
       </c>
       <c r="G88">
-        <v>-10.85745500235786</v>
+        <v>-14.91814036591804</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>3.440348896810894</v>
       </c>
       <c r="E89">
-        <v>-30.45262217914044</v>
+        <v>-37.10101072402152</v>
       </c>
       <c r="F89">
-        <v>-6.648650679137642</v>
+        <v>-8.076867555946286</v>
       </c>
       <c r="G89">
-        <v>-12.1601314982423</v>
+        <v>-15.30030974297151</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>3.289014400517649</v>
       </c>
       <c r="E90">
-        <v>-31.68013298602961</v>
+        <v>-37.05628977895877</v>
       </c>
       <c r="F90">
-        <v>-7.04408898064907</v>
+        <v>-8.23045377191969</v>
       </c>
       <c r="G90">
-        <v>-11.5546161663819</v>
+        <v>-15.49329799518332</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>3.098131007513663</v>
       </c>
       <c r="E91">
-        <v>-33.70967956018026</v>
+        <v>-39.25467597801141</v>
       </c>
       <c r="F91">
-        <v>-6.96090918263188</v>
+        <v>-7.626597000451079</v>
       </c>
       <c r="G91">
-        <v>-10.84271314307148</v>
+        <v>-15.08854242118818</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>2.865339709821282</v>
       </c>
       <c r="E92">
-        <v>-34.43499618504081</v>
+        <v>-39.93862046433788</v>
       </c>
       <c r="F92">
-        <v>-6.586379758469042</v>
+        <v>-7.783508998846903</v>
       </c>
       <c r="G92">
-        <v>-11.09914468999789</v>
+        <v>-15.82307136798674</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>2.585248877170307</v>
       </c>
       <c r="E93">
-        <v>-37.01259679749577</v>
+        <v>-40.3196032468402</v>
       </c>
       <c r="F93">
-        <v>-6.929921996763913</v>
+        <v>-7.284416749243485</v>
       </c>
       <c r="G93">
-        <v>-11.76742465473733</v>
+        <v>-17.45284962642441</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>2.257257668938939</v>
       </c>
       <c r="E94">
-        <v>-37.92220193633546</v>
+        <v>-42.46215562561526</v>
       </c>
       <c r="F94">
-        <v>-7.121802221772641</v>
+        <v>-8.249923060591144</v>
       </c>
       <c r="G94">
-        <v>-11.6598815828941</v>
+        <v>-15.51927915657552</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>1.878023573277053</v>
       </c>
       <c r="E95">
-        <v>-39.40610814882791</v>
+        <v>-42.92065682618087</v>
       </c>
       <c r="F95">
-        <v>-7.204615391870407</v>
+        <v>-7.719178468635274</v>
       </c>
       <c r="G95">
-        <v>-12.51121816322754</v>
+        <v>-16.66016929195577</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>1.445708930878406</v>
       </c>
       <c r="E96">
-        <v>-41.66528005448551</v>
+        <v>-45.94232639253899</v>
       </c>
       <c r="F96">
-        <v>-6.712010001696628</v>
+        <v>-7.890076173970344</v>
       </c>
       <c r="G96">
-        <v>-12.50795065478028</v>
+        <v>-15.62769786771388</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>0.9649721407652264</v>
       </c>
       <c r="E97">
-        <v>-42.59821136293871</v>
+        <v>-47.44192603170503</v>
       </c>
       <c r="F97">
-        <v>-6.742692324175874</v>
+        <v>-7.554203823423947</v>
       </c>
       <c r="G97">
-        <v>-12.07107120214482</v>
+        <v>-16.89830179841386</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>0.4287727918852594</v>
       </c>
       <c r="E98">
-        <v>-45.31971329393541</v>
+        <v>-48.49403319061809</v>
       </c>
       <c r="F98">
-        <v>-7.073722097959337</v>
+        <v>-7.698045100973172</v>
       </c>
       <c r="G98">
-        <v>-12.91454854736803</v>
+        <v>-16.47291324934521</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-0.1394174385150158</v>
       </c>
       <c r="E99">
-        <v>-47.42796701057638</v>
+        <v>-50.21588354136957</v>
       </c>
       <c r="F99">
-        <v>-7.049768545988314</v>
+        <v>-6.607222516095661</v>
       </c>
       <c r="G99">
-        <v>-12.67839409186966</v>
+        <v>-16.44480175189849</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-0.7606692344088759</v>
       </c>
       <c r="E100">
-        <v>-48.50143498138363</v>
+        <v>-50.68839923687042</v>
       </c>
       <c r="F100">
-        <v>-7.463754419328412</v>
+        <v>-7.827598183753301</v>
       </c>
       <c r="G100">
-        <v>-12.9134163407936</v>
+        <v>-17.88456462801861</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-1.369840976600904</v>
       </c>
       <c r="E101">
-        <v>-49.8389367613266</v>
+        <v>-55.11173339926769</v>
       </c>
       <c r="F101">
-        <v>-7.133576679327454</v>
+        <v>-7.526190837265175</v>
       </c>
       <c r="G101">
-        <v>-13.6366265323934</v>
+        <v>-17.69495313225685</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-2.039773417061899</v>
       </c>
       <c r="E102">
-        <v>-52.57380221911993</v>
+        <v>-56.49984766895739</v>
       </c>
       <c r="F102">
-        <v>-7.153419722594953</v>
+        <v>-7.545220251618616</v>
       </c>
       <c r="G102">
-        <v>-13.27606674134752</v>
+        <v>-18.56684488984362</v>
       </c>
     </row>
   </sheetData>
